--- a/docs/templates/yoY_report_template.xlsx
+++ b/docs/templates/yoY_report_template.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対象確認" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変化表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="差分詳細" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マツダ比較" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="使い方" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="対象確認" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="変化表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="差分詳細" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="分析" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="マツダ比較" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="要確認" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'対象確認'!$A$5:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'変化表'!$A$5:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'差分詳細'!$A$5:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'分析'!$A$5:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'マツダ比較'!$A$5:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'要確認'!$A$5:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -540,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -607,6 +614,27 @@
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>ファイル名: 事業等のリスク_YoY_YYYYMMDD.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>変更種別（差分詳細・変化表）: CLI の分類 新設→追加、削除→削除、修正・改題・統合・分割→改訂、一致・移動→変更「あり」「軽微」なら改訂／「なし」なら載せない。判断できないものは要確認へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>文字数増減率は 週次要約.md の値を転記（再計算しない）。値がなければ空欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>各シートの見出し行（5行目）にオートフィルタ付き。</t>
         </is>
       </c>
     </row>
@@ -749,6 +777,7 @@
       <c r="H6" s="8" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A5:H6"/>
   <mergeCells count="3">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A2:H2"/>
@@ -885,6 +914,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:H6"/>
   <mergeCells count="3">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A2:H2"/>
@@ -1123,6 +1153,7 @@
       <c r="I8" s="8" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A5:I8"/>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:I4"/>
@@ -1307,6 +1338,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:F8"/>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -1427,6 +1459,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:F6"/>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -1547,6 +1580,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:F6"/>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
